--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:08</t>
+    <t xml:space="preserve">2026-09-09 23:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:02</t>
+    <t xml:space="preserve">2026-09-17 13:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:59</t>
+    <t xml:space="preserve">2026-09-23 12:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:28</t>
+    <t xml:space="preserve">2026-10-02 13:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:47</t>
+    <t xml:space="preserve">2026-10-05 10:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -679,7 +679,7 @@
         <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>657653.62</v>
+        <v>657653.63</v>
       </c>
     </row>
     <row r="9">
@@ -968,7 +968,7 @@
         <v>2020</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>588354.12</v>
+        <v>588354.13</v>
       </c>
     </row>
     <row r="26">
